--- a/data/aa2_3_h.xlsx
+++ b/data/aa2_3_h.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GinrutPrices\Output\A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\odelyas\Desktop\AA\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -15,16 +15,16 @@
     <sheet name="AA.2.3" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">AA.2.3!$1:$7</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">AA.2.3!$5:$8</definedName>
   </definedNames>
   <calcPr calcId="162913" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="122">
-  <si>
-    <t>הופק לאחרונה עבור ירחון מחירים מס' 4/2026, הלשכה המרכזית לסטטיסטיקה</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="125">
+  <si>
+    <t>הופק לאחרונה עבור ירחון מחירים מס' 7/2026, הלשכה המרכזית לסטטיסטיקה</t>
   </si>
   <si>
     <t>הבסיס: אוקטובר 2017 - נובמבר 2017=414.5</t>
@@ -368,6 +368,15 @@
   </si>
   <si>
     <t>פברואר 2026 - מרס 2026</t>
+  </si>
+  <si>
+    <t>מרס 2026 - אפריל 2026</t>
+  </si>
+  <si>
+    <t>אפריל 2026 - מאי 2026</t>
+  </si>
+  <si>
+    <t>מאי 2026 - יוני 2026</t>
   </si>
   <si>
     <t>(1)   מדד זה משמש כאינדיקטור לשינויים במחירי דירות לפי מחוזות ואינו חלק ממסגרת מדד המחירים לצרכן.</t>
@@ -997,22 +1006,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M118"/>
+  <dimension ref="A1:M121"/>
   <sheetFormatPr defaultColWidth="4.5703125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" style="7" customWidth="1"/>
-    <col min="2" max="2" width="7.28515625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="8.42578125" style="7" customWidth="1"/>
-    <col min="4" max="4" width="7.28515625" style="7" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" style="7" customWidth="1"/>
-    <col min="6" max="6" width="7.28515625" style="7" customWidth="1"/>
-    <col min="7" max="7" width="8.42578125" style="7" customWidth="1"/>
-    <col min="8" max="8" width="7.28515625" style="7" customWidth="1"/>
-    <col min="9" max="9" width="8.42578125" style="7" customWidth="1"/>
-    <col min="10" max="10" width="7.28515625" style="7" customWidth="1"/>
-    <col min="11" max="11" width="8.42578125" style="7" customWidth="1"/>
-    <col min="12" max="12" width="7.28515625" style="7" customWidth="1"/>
-    <col min="13" max="13" width="25.42578125" style="7" customWidth="1"/>
+    <col min="1" max="1" width="8.140625" style="7" customWidth="1"/>
+    <col min="2" max="2" width="7" style="7" customWidth="1"/>
+    <col min="3" max="3" width="8.140625" style="7" customWidth="1"/>
+    <col min="4" max="4" width="7" style="7" customWidth="1"/>
+    <col min="5" max="5" width="8.140625" style="7" customWidth="1"/>
+    <col min="6" max="6" width="7" style="7" customWidth="1"/>
+    <col min="7" max="7" width="8.140625" style="7" customWidth="1"/>
+    <col min="8" max="8" width="7" style="7" customWidth="1"/>
+    <col min="9" max="9" width="8.140625" style="7" customWidth="1"/>
+    <col min="10" max="10" width="7" style="7" customWidth="1"/>
+    <col min="11" max="11" width="8.140625" style="7" customWidth="1"/>
+    <col min="12" max="12" width="7" style="7" customWidth="1"/>
+    <col min="13" max="13" width="29" style="7" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -1034,7 +1043,7 @@
     </row>
     <row r="3" spans="1:13" ht="18.75">
       <c r="A3" s="17" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
@@ -5185,40 +5194,40 @@
       </c>
     </row>
     <row r="107" spans="1:13">
-      <c r="A107" s="5">
+      <c r="A107" s="4">
         <v>0.2</v>
       </c>
-      <c r="B107" s="5">
+      <c r="B107" s="4">
         <v>580.29999999999995</v>
       </c>
-      <c r="C107" s="11">
+      <c r="C107" s="10">
         <v>0.3</v>
       </c>
-      <c r="D107" s="5">
+      <c r="D107" s="4">
         <v>569.79999999999995</v>
       </c>
-      <c r="E107" s="11">
+      <c r="E107" s="10">
         <v>-0.5</v>
       </c>
-      <c r="F107" s="5">
+      <c r="F107" s="4">
         <v>586.4</v>
       </c>
-      <c r="G107" s="11">
+      <c r="G107" s="10">
         <v>0.3</v>
       </c>
-      <c r="H107" s="5">
+      <c r="H107" s="4">
         <v>626</v>
       </c>
-      <c r="I107" s="11">
+      <c r="I107" s="10">
         <v>0</v>
       </c>
-      <c r="J107" s="5">
+      <c r="J107" s="4">
         <v>662.9</v>
       </c>
-      <c r="K107" s="11">
+      <c r="K107" s="10">
         <v>-0.6</v>
       </c>
-      <c r="L107" s="5">
+      <c r="L107" s="4">
         <v>597.4</v>
       </c>
       <c r="M107" s="14" t="s">
@@ -5226,152 +5235,224 @@
       </c>
     </row>
     <row r="108" spans="1:13">
-      <c r="A108" s="5">
-        <v>0.2</v>
-      </c>
-      <c r="B108" s="5">
-        <v>581.5</v>
-      </c>
-      <c r="C108" s="11">
+      <c r="A108" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="B108" s="4">
+        <v>582</v>
+      </c>
+      <c r="C108" s="10">
         <v>-0.8</v>
       </c>
-      <c r="D108" s="5">
+      <c r="D108" s="4">
         <v>565.20000000000005</v>
       </c>
-      <c r="E108" s="11">
-        <v>0.6</v>
-      </c>
-      <c r="F108" s="5">
-        <v>589.9</v>
-      </c>
-      <c r="G108" s="11">
-        <v>0.3</v>
-      </c>
-      <c r="H108" s="5">
-        <v>627.9</v>
-      </c>
-      <c r="I108" s="11">
-        <v>0.9</v>
-      </c>
-      <c r="J108" s="5">
-        <v>668.9</v>
-      </c>
-      <c r="K108" s="11">
-        <v>-1</v>
-      </c>
-      <c r="L108" s="5">
-        <v>591.4</v>
+      <c r="E108" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="F108" s="4">
+        <v>590.5</v>
+      </c>
+      <c r="G108" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="H108" s="4">
+        <v>629.1</v>
+      </c>
+      <c r="I108" s="10">
+        <v>1</v>
+      </c>
+      <c r="J108" s="4">
+        <v>669.5</v>
+      </c>
+      <c r="K108" s="10">
+        <v>-1.4</v>
+      </c>
+      <c r="L108" s="4">
+        <v>589</v>
       </c>
       <c r="M108" s="14" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="109" spans="1:13">
-      <c r="A109" s="5">
+      <c r="A109" s="4">
+        <v>-0.4</v>
+      </c>
+      <c r="B109" s="4">
+        <v>579.70000000000005</v>
+      </c>
+      <c r="C109" s="10">
+        <v>1.3</v>
+      </c>
+      <c r="D109" s="4">
+        <v>572.5</v>
+      </c>
+      <c r="E109" s="10">
         <v>0</v>
       </c>
-      <c r="B109" s="5">
-        <v>581.5</v>
-      </c>
-      <c r="C109" s="11">
-        <v>1.2</v>
-      </c>
-      <c r="D109" s="5">
-        <v>572</v>
-      </c>
-      <c r="E109" s="11">
-        <v>-0.2</v>
-      </c>
-      <c r="F109" s="5">
-        <v>588.70000000000005</v>
-      </c>
-      <c r="G109" s="11">
-        <v>0.1</v>
-      </c>
-      <c r="H109" s="5">
-        <v>628.5</v>
-      </c>
-      <c r="I109" s="11">
-        <v>-0.1</v>
-      </c>
-      <c r="J109" s="5">
-        <v>668.2</v>
-      </c>
-      <c r="K109" s="11">
+      <c r="F109" s="4">
+        <v>590.5</v>
+      </c>
+      <c r="G109" s="10">
         <v>0.4</v>
       </c>
-      <c r="L109" s="5">
-        <v>593.79999999999995</v>
+      <c r="H109" s="4">
+        <v>631.6</v>
+      </c>
+      <c r="I109" s="10">
+        <v>-0.3</v>
+      </c>
+      <c r="J109" s="4">
+        <v>667.5</v>
+      </c>
+      <c r="K109" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="L109" s="4">
+        <v>591.9</v>
       </c>
       <c r="M109" s="14" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="110" spans="1:13">
-      <c r="A110" s="6"/>
-      <c r="B110" s="8"/>
-      <c r="C110" s="8"/>
-      <c r="D110" s="8"/>
-      <c r="E110" s="8"/>
-      <c r="F110" s="8"/>
-      <c r="G110" s="8"/>
-      <c r="H110" s="8"/>
-      <c r="I110" s="8"/>
-      <c r="J110" s="8"/>
-      <c r="K110" s="8"/>
-      <c r="L110" s="8"/>
-      <c r="M110" s="8"/>
+      <c r="A110" s="5">
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="B110" s="5">
+        <v>573.29999999999995</v>
+      </c>
+      <c r="C110" s="11">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D110" s="5">
+        <v>578.79999999999995</v>
+      </c>
+      <c r="E110" s="11">
+        <v>-0.1</v>
+      </c>
+      <c r="F110" s="5">
+        <v>589.9</v>
+      </c>
+      <c r="G110" s="11">
+        <v>-1.6</v>
+      </c>
+      <c r="H110" s="5">
+        <v>621.5</v>
+      </c>
+      <c r="I110" s="11">
+        <v>-0.3</v>
+      </c>
+      <c r="J110" s="5">
+        <v>665.5</v>
+      </c>
+      <c r="K110" s="11">
+        <v>-2.6</v>
+      </c>
+      <c r="L110" s="5">
+        <v>576.5</v>
+      </c>
+      <c r="M110" s="14" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="111" spans="1:13">
-      <c r="A111" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="B111" s="15"/>
-      <c r="C111" s="15"/>
-      <c r="D111" s="15"/>
-      <c r="E111" s="15"/>
-      <c r="F111" s="15"/>
-      <c r="G111" s="15"/>
-      <c r="H111" s="15"/>
-      <c r="I111" s="15"/>
-      <c r="J111" s="15"/>
-      <c r="K111" s="15"/>
-      <c r="L111" s="15"/>
-      <c r="M111" s="15"/>
+      <c r="A111" s="5">
+        <v>-0.3</v>
+      </c>
+      <c r="B111" s="5">
+        <v>571.6</v>
+      </c>
+      <c r="C111" s="11">
+        <v>-2.5</v>
+      </c>
+      <c r="D111" s="5">
+        <v>564.29999999999995</v>
+      </c>
+      <c r="E111" s="11">
+        <v>-0.3</v>
+      </c>
+      <c r="F111" s="5">
+        <v>588.1</v>
+      </c>
+      <c r="G111" s="11">
+        <v>-0.6</v>
+      </c>
+      <c r="H111" s="5">
+        <v>617.79999999999995</v>
+      </c>
+      <c r="I111" s="11">
+        <v>-0.6</v>
+      </c>
+      <c r="J111" s="5">
+        <v>661.5</v>
+      </c>
+      <c r="K111" s="11">
+        <v>-1.6</v>
+      </c>
+      <c r="L111" s="5">
+        <v>567.29999999999995</v>
+      </c>
+      <c r="M111" s="14" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="112" spans="1:13">
-      <c r="A112" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="B112" s="15"/>
-      <c r="C112" s="15"/>
-      <c r="D112" s="15"/>
-      <c r="E112" s="15"/>
-      <c r="F112" s="15"/>
-      <c r="G112" s="15"/>
-      <c r="H112" s="15"/>
-      <c r="I112" s="15"/>
-      <c r="J112" s="15"/>
-      <c r="K112" s="15"/>
-      <c r="L112" s="15"/>
-      <c r="M112" s="15"/>
+      <c r="A112" s="5">
+        <v>0.7</v>
+      </c>
+      <c r="B112" s="5">
+        <v>575.6</v>
+      </c>
+      <c r="C112" s="11">
+        <v>-0.7</v>
+      </c>
+      <c r="D112" s="5">
+        <v>560.29999999999995</v>
+      </c>
+      <c r="E112" s="11">
+        <v>-1</v>
+      </c>
+      <c r="F112" s="5">
+        <v>582.20000000000005</v>
+      </c>
+      <c r="G112" s="11">
+        <v>1.5</v>
+      </c>
+      <c r="H112" s="5">
+        <v>627.1</v>
+      </c>
+      <c r="I112" s="11">
+        <v>0.9</v>
+      </c>
+      <c r="J112" s="5">
+        <v>667.5</v>
+      </c>
+      <c r="K112" s="11">
+        <v>1.8</v>
+      </c>
+      <c r="L112" s="5">
+        <v>577.5</v>
+      </c>
+      <c r="M112" s="14" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="113" spans="1:13">
-      <c r="A113" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="B113" s="15"/>
-      <c r="C113" s="15"/>
-      <c r="D113" s="15"/>
-      <c r="E113" s="15"/>
-      <c r="F113" s="15"/>
-      <c r="G113" s="15"/>
-      <c r="H113" s="15"/>
-      <c r="I113" s="15"/>
-      <c r="J113" s="15"/>
-      <c r="K113" s="15"/>
-      <c r="L113" s="15"/>
-      <c r="M113" s="15"/>
+      <c r="A113" s="6"/>
+      <c r="B113" s="8"/>
+      <c r="C113" s="8"/>
+      <c r="D113" s="8"/>
+      <c r="E113" s="8"/>
+      <c r="F113" s="8"/>
+      <c r="G113" s="8"/>
+      <c r="H113" s="8"/>
+      <c r="I113" s="8"/>
+      <c r="J113" s="8"/>
+      <c r="K113" s="8"/>
+      <c r="L113" s="8"/>
+      <c r="M113" s="8"/>
     </row>
     <row r="114" spans="1:13">
       <c r="A114" s="15" t="s">
@@ -5458,6 +5539,57 @@
       <c r="L118" s="15"/>
       <c r="M118" s="15"/>
     </row>
+    <row r="119" spans="1:13">
+      <c r="A119" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="B119" s="15"/>
+      <c r="C119" s="15"/>
+      <c r="D119" s="15"/>
+      <c r="E119" s="15"/>
+      <c r="F119" s="15"/>
+      <c r="G119" s="15"/>
+      <c r="H119" s="15"/>
+      <c r="I119" s="15"/>
+      <c r="J119" s="15"/>
+      <c r="K119" s="15"/>
+      <c r="L119" s="15"/>
+      <c r="M119" s="15"/>
+    </row>
+    <row r="120" spans="1:13">
+      <c r="A120" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B120" s="15"/>
+      <c r="C120" s="15"/>
+      <c r="D120" s="15"/>
+      <c r="E120" s="15"/>
+      <c r="F120" s="15"/>
+      <c r="G120" s="15"/>
+      <c r="H120" s="15"/>
+      <c r="I120" s="15"/>
+      <c r="J120" s="15"/>
+      <c r="K120" s="15"/>
+      <c r="L120" s="15"/>
+      <c r="M120" s="15"/>
+    </row>
+    <row r="121" spans="1:13">
+      <c r="A121" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="B121" s="15"/>
+      <c r="C121" s="15"/>
+      <c r="D121" s="15"/>
+      <c r="E121" s="15"/>
+      <c r="F121" s="15"/>
+      <c r="G121" s="15"/>
+      <c r="H121" s="15"/>
+      <c r="I121" s="15"/>
+      <c r="J121" s="15"/>
+      <c r="K121" s="15"/>
+      <c r="L121" s="15"/>
+      <c r="M121" s="15"/>
+    </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="A1:M1"/>
@@ -5470,14 +5602,14 @@
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="I6:J6"/>
     <mergeCell ref="K6:L6"/>
+    <mergeCell ref="A119:M119"/>
+    <mergeCell ref="A120:M120"/>
+    <mergeCell ref="A121:M121"/>
+    <mergeCell ref="A114:M114"/>
+    <mergeCell ref="A115:M115"/>
     <mergeCell ref="A116:M116"/>
     <mergeCell ref="A117:M117"/>
     <mergeCell ref="A118:M118"/>
-    <mergeCell ref="A111:M111"/>
-    <mergeCell ref="A112:M112"/>
-    <mergeCell ref="A113:M113"/>
-    <mergeCell ref="A114:M114"/>
-    <mergeCell ref="A115:M115"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.5"/>
